--- a/corpus/xlsx/level-074/template.xlsx
+++ b/corpus/xlsx/level-074/template.xlsx
@@ -19,17 +19,17 @@
     <sheet name="Region 10 山田" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="ItemRange1">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange2">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange3">'Report'!$A$40:$D$40</definedName>
-    <definedName name="ItemRange4">'Report'!$A$40:$D$40</definedName>
+    <definedName name="ItemRange1">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange2">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange3">'Report'!$A$40:$D$41</definedName>
+    <definedName name="ItemRange4">'Report'!$A$40:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <si>
     <r>
       <rPr>
@@ -127,7 +127,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -168,14 +176,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -201,7 +201,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -217,15 +225,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">u</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
     </r>
     <r>
       <rPr>
@@ -257,15 +265,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -283,7 +283,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -324,14 +332,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -357,7 +357,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -406,14 +414,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -439,7 +439,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -495,15 +503,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -521,7 +521,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -577,15 +585,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
   <si>
@@ -779,39 +779,31 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">#e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ac</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">h i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">te</t>
+      <t xml:space="preserve">{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
     </r>
     <r>
       <rPr>
@@ -827,15 +819,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">}}{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{n</t>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
     </r>
     <r>
       <rPr>
@@ -851,7 +851,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">e}}</t>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -861,31 +861,55 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">u</t>
+      <t xml:space="preserve">{d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">te</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">qu</t>
     </r>
     <r>
       <rPr>
@@ -901,39 +925,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">y</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">ti</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ty}</t>
     </r>
   </si>
   <si>
@@ -951,6 +951,80 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">pr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ic</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
       <t xml:space="preserve">{</t>
     </r>
     <r>
@@ -959,55 +1033,71 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">p</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">1]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">am</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -1971,7 +2061,7 @@
     <xdr:ext cx="914400" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2002,7 +2092,7 @@
     <xdr:ext cx="960120" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2033,7 +2123,7 @@
     <xdr:ext cx="1005840" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2064,7 +2154,7 @@
     <xdr:ext cx="1051560" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2095,7 +2185,7 @@
     <xdr:ext cx="1097280" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2126,7 +2216,7 @@
     <xdr:ext cx="1143000" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2157,7 +2247,7 @@
     <xdr:ext cx="1188720" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2188,7 +2278,7 @@
     <xdr:ext cx="1234440" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2219,7 +2309,7 @@
     <xdr:ext cx="1280160" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2250,7 +2340,7 @@
     <xdr:ext cx="1325880" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2275,8 +2365,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D40" totalsRowShown="0">
-  <autoFilter ref="A39:D40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Items" displayName="Items" ref="A39:D41" totalsRowShown="0">
+  <autoFilter ref="A39:D41"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Name"/>
     <tableColumn id="2" name="Quantity"/>
@@ -2289,7 +2379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2616,14 +2706,14 @@
         <f>B40*C40</f>
         <v>0</v>
       </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{/each}}</t>
-        </is>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A39:D40"/>
+  <autoFilter ref="A39:D41"/>
   <mergeCells count="10">
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
@@ -2636,17 +2726,17 @@
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A24:C24"/>
   </mergeCells>
-  <conditionalFormatting sqref="B40:B40">
+  <conditionalFormatting sqref="B40:B41">
     <cfRule type="cellIs" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="B40:B41">
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C40">
+    <dataValidation type="whole" operator="between" allowBlank="1" sqref="C40:C41">
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
@@ -2665,7 +2755,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2689,7 +2779,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2713,7 +2803,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2737,7 +2827,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2761,7 +2851,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2785,7 +2875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2809,7 +2899,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2833,7 +2923,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2857,7 +2947,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2881,7 +2971,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2905,7 +2995,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
